--- a/Zinc/5. Cluster analysis/Typology Plots/Sites_with_many_typologies.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Sites_with_many_typologies.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -26,13 +26,13 @@
     <t xml:space="preserve">BCK0.9</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs, PD Tribs, Main Stem</t>
+    <t xml:space="preserve">Perennial Tribs, Developed Tribs, Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">PD Tribs, Main Stem</t>
+    <t xml:space="preserve">Developed Tribs, Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.3</t>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">BSL2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs, PD Tribs</t>
+    <t xml:space="preserve">Perennial Tribs, Developed Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL3.1</t>
@@ -56,13 +56,25 @@
     <t xml:space="preserve">BSL3.3</t>
   </si>
   <si>
+    <t xml:space="preserve">BSL4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs, Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Downtown</t>
   </si>
   <si>
     <t xml:space="preserve">EFK10.0</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs, Main Stem</t>
+    <t xml:space="preserve">Perennial Tribs, Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">EFK13.8</t>
@@ -92,13 +104,28 @@
     <t xml:space="preserve">MCA3.1</t>
   </si>
   <si>
+    <t xml:space="preserve">Perennial Tribs, Developed Tribs, Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial Tribs, Pooled Water</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCA4</t>
   </si>
   <si>
+    <t xml:space="preserve">MTN1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Tribs, Pooled Water</t>
+  </si>
+  <si>
     <t xml:space="preserve">MTN4</t>
   </si>
   <si>
-    <t xml:space="preserve">NP Tribs, P Tribs, PD Tribs</t>
+    <t xml:space="preserve">Non-Perennial Tribs, Perennial Tribs, Developed Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">NBO2</t>
@@ -107,7 +134,10 @@
     <t xml:space="preserve">NBO3</t>
   </si>
   <si>
-    <t xml:space="preserve">NP Tribs, P Tribs</t>
+    <t xml:space="preserve">Non-Perennial Tribs, Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO5</t>
   </si>
   <si>
     <t xml:space="preserve">Pinhook Branch</t>
@@ -117,6 +147,12 @@
   </si>
   <si>
     <t xml:space="preserve">WBK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-Perennial Tribs, Perennial Tribs, Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK3</t>
   </si>
 </sst>
 </file>
@@ -549,21 +585,21 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -574,7 +610,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -582,10 +618,10 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -596,95 +632,95 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -695,51 +731,128 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/5. Cluster analysis/Typology Plots/Sites_with_many_typologies.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Sites_with_many_typologies.xlsx
@@ -26,13 +26,13 @@
     <t xml:space="preserve">BCK0.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs, Developed Tribs, Main Stem</t>
+    <t xml:space="preserve">Perennial, Developed Perennial, Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed Tribs, Main Stem</t>
+    <t xml:space="preserve">Developed Perennial, Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.3</t>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">BSL2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs, Developed Tribs</t>
+    <t xml:space="preserve">Perennial, Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">BSL3.1</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">BSL4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs, Pooled Water</t>
+    <t xml:space="preserve">Perennial, Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.2</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">EFK10.0</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs, Main Stem</t>
+    <t xml:space="preserve">Perennial, Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">EFK13.8</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">MCA3.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs, Developed Tribs, Pooled Water</t>
+    <t xml:space="preserve">Perennial, Developed Perennial, Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">MCA3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs, Pooled Water</t>
+    <t xml:space="preserve">Non-Perennial, Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">MCA4</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">MTN1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed Tribs, Pooled Water</t>
+    <t xml:space="preserve">Developed Perennial, Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">MTN4</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs, Perennial Tribs, Developed Tribs</t>
+    <t xml:space="preserve">Non-Perennial, Perennial, Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">NBO2</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">NBO3</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs, Perennial Tribs</t>
+    <t xml:space="preserve">Non-Perennial, Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">NBO5</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">WBK2</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs, Perennial Tribs, Pooled Water</t>
+    <t xml:space="preserve">Non-Perennial, Perennial, Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">WBK3</t>
